--- a/data/raw/synfuel_dict.xlsx
+++ b/data/raw/synfuel_dict.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11012"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haukeschlesier/FFEI/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haukeschlesier/FFEI/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{418F132D-4B08-4640-9CB2-0201A4F715EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FCCCABD-B222-6B45-B274-5C114AAC0605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="760" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="49">
   <si>
     <t>diesel</t>
   </si>
@@ -137,6 +150,36 @@
   </si>
   <si>
     <t>peat</t>
+  </si>
+  <si>
+    <t>market for biomethane, burned in gas motor, for storage</t>
+  </si>
+  <si>
+    <t>market for methane, synthetic, medium pressure</t>
+  </si>
+  <si>
+    <t>market for methane, synthetic, high pressure</t>
+  </si>
+  <si>
+    <t>market for methane, synthetic, low pressure</t>
+  </si>
+  <si>
+    <t>market for methane, synthetic, liquefied</t>
+  </si>
+  <si>
+    <t>methane, synthetic, burned in gas motor</t>
+  </si>
+  <si>
+    <t>bio-based</t>
+  </si>
+  <si>
+    <t>synthetic</t>
+  </si>
+  <si>
+    <t>water pump operation, electric</t>
+  </si>
+  <si>
+    <t>water pump operation</t>
   </si>
 </sst>
 </file>
@@ -213,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -227,9 +270,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -536,10 +576,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:Z3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -609,13 +652,16 @@
       <c r="X1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="Y1" s="7" t="s">
+      <c r="Y1" s="6" t="s">
         <v>38</v>
       </c>
+      <c r="Z1" s="4" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>0</v>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
@@ -678,7 +724,7 @@
         <v>25</v>
       </c>
       <c r="V2" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="W2" t="s">
         <v>23</v>
@@ -690,9 +736,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <v>1</v>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -706,15 +752,36 @@
       <c r="F3" t="s">
         <v>17</v>
       </c>
+      <c r="H3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" t="s">
+        <v>40</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="S3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
+      <c r="V3" t="s">
+        <v>44</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="X3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>47</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
